--- a/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yasmine et papa sont au jardin. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi. Yasmine dit : chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Yasmine et papa sont au jardin. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit. On va passer le ballon. Ensuite, chacun a un lancer. Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi. Chacun un lancer. Ils se passent encore le ballon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine et papa sont au jardin. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit.
+papa|On va passer le ballon. Ensuite, chacun a un lancer.
+narrateur|Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi.
+enfant-f|Chacun un lancer.
+narrateur|Ils se passent encore le ballon.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine joue au basket. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Yasmine a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Yasmine essuie ses mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Ils se passent encore le ballon.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Yasmine joue au basket. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Yasmine a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa range le ballon. Yasmine essuie ses mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yasmine lance au panier</t>
+          <t>Nina lance au panier</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Des gouttes brillent sur la salade. Nina et papa se passent le ballon. Chacun a un lancer vers le petit panier.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yasmine et papa sont au jardin. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit. On va passer le ballon. Ensuite, chacun a un lancer. Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi. Chacun un lancer. Ils se passent encore le ballon.</t>
+          <t>Les feuilles de salade portent des gouttes. Une goutte glisse et tombe. Le sol du jardin est frais. Un tuyau vert est enroulé. Une coccinelle marche sur une feuille. Nina, viens voir la coccinelle. En ce moment, Nina s'accroupit. La coccinelle est rouge et ronde. Elle est petite, papa. Oui. Toute petite. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit dans l'herbe. On va passer le ballon. Ensuite, chacun a un lancer. Nina passe le ballon à papa. Papa le passe. C'est le lancer de Nina. Nina lance vers le panier. Le ballon rentre. Dedans ! Bravo. Tu as visé le panier. Papa a son lancer. Il lance aussi. Chacun un lancer. Oui. Chacun un lancer. Ils se passent encore le ballon. Nina attend. Puis elle lance. Les pieds restent près du panier. Nina reste près du panier. Le ballon est un peu humide. Encore, papa. Oui. D'abord on passe. Nina passe. Papa passe. Chacun a un lancer. Bravo, Nina. La coccinelle a disparu. Une goutte brille encore. Tu as passé. Tu as lancé. Le ballon est orange. Oui. Et le panier est bas. Nina tient le ballon. C'est ton lancer. Elle lance. Le filet bouge. Bien joué. Chacun a un lancer. Nina pose le pied près du panier. Les pieds restent ici. Près du panier. Oui. On passe, puis on lance. Nina passe le ballon. Papa le rend. Nina lance. Le ballon rentre encore. Bravo. Chacun a un lancer. Une feuille de salade tremble. Une goutte est tombée. Oui. Et toi, tu as bien visé. Nina attend. Papa lance. Puis Nina lance. Tu as passé. Tu as lancé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine et papa sont au jardin. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit.
-papa|On va passer le ballon. Ensuite, chacun a un lancer.
-narrateur|Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi.
+          <t>narrateur|Les feuilles de salade portent des gouttes.
+narrateur|Une goutte glisse et tombe.
+narrateur|Le sol du jardin est frais.
+narrateur|Un tuyau vert est enroulé.
+narrateur|Une coccinelle marche sur une feuille.
+papa|Nina, viens voir la coccinelle.
+narrateur|En ce moment, Nina s'accroupit.
+narrateur|La coccinelle est rouge et ronde.
+enfant-f|Elle est petite, papa.
+papa|Oui. Toute petite.
+narrateur|Un petit panier est accroché bas.
+narrateur|Papa donne le ballon orange.
+narrateur|Il rebondit dans l'herbe.
+papa|On va passer le ballon.
+papa|Ensuite, chacun a un lancer.
+narrateur|Nina passe le ballon à papa.
+narrateur|Papa le passe.
+papa|C'est le lancer de Nina.
+narrateur|Nina lance vers le panier.
+narrateur|Le ballon rentre.
+enfant-f|Dedans !
+papa|Bravo. Tu as visé le panier.
+narrateur|Papa a son lancer.
+narrateur|Il lance aussi.
 enfant-f|Chacun un lancer.
-narrateur|Ils se passent encore le ballon.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Oui. Chacun un lancer.
+narrateur|Ils se passent encore le ballon.
+narrateur|Nina attend. Puis elle lance.
+papa|Les pieds restent près du panier.
+narrateur|Nina reste près du panier.
+narrateur|Le ballon est un peu humide.
+enfant-f|Encore, papa.
+papa|Oui. D'abord on passe.
+narrateur|Nina passe. Papa passe.
+narrateur|Chacun a un lancer.
+papa|Bravo, Nina.
+narrateur|La coccinelle a disparu.
+narrateur|Une goutte brille encore.
+papa|Tu as passé. Tu as lancé.
+enfant-f|Le ballon est orange.
+papa|Oui. Et le panier est bas.
+narrateur|Nina tient le ballon.
+papa|C'est ton lancer.
+narrateur|Elle lance. Le filet bouge.
+papa|Bien joué. Chacun a un lancer.
+narrateur|Nina pose le pied près du panier.
+papa|Les pieds restent ici.
+enfant-f|Près du panier.
+papa|Oui. On passe, puis on lance.
+narrateur|Nina passe le ballon.
+narrateur|Papa le rend. Nina lance.
+narrateur|Le ballon rentre encore.
+papa|Bravo. Chacun a un lancer.
+narrateur|Une feuille de salade tremble.
+enfant-f|Une goutte est tombée.
+papa|Oui. Et toi, tu as bien visé.
+narrateur|Nina attend. Papa lance.
+narrateur|Puis Nina lance.
+papa|Tu as passé. Tu as lancé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Yasmine joue au basket. Que fait-elle ?</t>
+          <t>Nina joue au basket. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine joue au basket. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina joue au basket.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Yasmine a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
+          <t>Nina a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé. Tu as lancé. Chacun a eu un lancer. Le ballon est allé dans le panier. Oui. Bravo, Nina. Une goutte brille encore sur la salade. Le tuyau vert reste enroulé. Tu as visé le panier. Oui. Chacun un lancer. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,10 +1737,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Yasmine a passé le ballon. Elle a visé le panier. Chacun a eu un lancer.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a passé le ballon.
+narrateur|Elle a visé le panier.
+narrateur|Chacun a eu un lancer.
+papa|Tu as passé. Tu as lancé.
+papa|Chacun a eu un lancer.
+enfant-f|Le ballon est allé dans le panier.
+papa|Oui. Bravo, Nina.
+narrateur|Une goutte brille encore sur la salade.
+narrateur|Le tuyau vert reste enroulé.
+papa|Tu as visé le panier.
+enfant-f|Oui. Chacun un lancer.
+papa|Bravo, Nina.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Yasmine essuie ses mains.</t>
+          <t>Papa range le ballon. Nina essuie ses mains. Tu as fini de jouer ? Oui, papa. Bravo. On rentre. L'herbe est fraîche sous les pieds. Ils rentrent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1915,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Yasmine essuie ses mains.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon.
+narrateur|Nina essuie ses mains.
+papa|Tu as fini de jouer ?
+enfant-f|Oui, papa.
+papa|Bravo. On rentre.
+narrateur|L'herbe est fraîche sous les pieds.
+narrateur|Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le ballon orange est rangé. Nina a passé. Elle a visé le panier. Bravo, Nina. Tu as bien joué. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,10 +2088,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le ballon orange est rangé.
+narrateur|Nina a passé. Elle a visé le panier.
+papa|Bravo, Nina. Tu as bien joué.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine et papa sont au jardin. Un petit &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt; est accroché bas. Papa donne le ballon orange. Il rebondit. Papa dit : on va passer le ballon. Ensuite, chacun a un lancer. Yasmine passe le ballon à papa. Papa le passe. C'est le lancer de Yasmine. Yasmine lance vers le panier. Le ballon rentre. Papa a son lancer. Il lance aussi. Yasmine dit : chacun un lancer. Ils se passent encore le ballon.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles de salade portent des gouttes. Une goutte glisse et tombe. Le sol du jardin est frais. Un tuyau vert est enroulé. Une coccinelle marche sur une feuille. Nina, viens voir la coccinelle. En ce moment, Nina s'accroupit. La coccinelle est rouge et ronde. Elle est petite, papa. Oui. Toute petite. Un petit panier est accroché bas. Papa donne le ballon orange. Il rebondit dans l'herbe. On va passer le ballon. Ensuite, chacun a un lancer. Nina passe le ballon à papa. Papa le passe. C'est le lancer de Nina. Nina lance vers le panier. Le ballon rentre. Dedans ! Bravo. Tu as visé le panier. Papa a son lancer. Il lance aussi. Chacun un lancer. Oui. Chacun un lancer. Ils se passent encore le ballon. Nina attend. Puis elle lance. Les pieds restent près du panier. Nina reste près du panier. Le ballon est un peu humide. Encore, papa. Oui. D'abord on passe. Nina passe. Papa passe. Chacun a un lancer. Bravo, Nina. La coccinelle a disparu. Une goutte brille encore. Tu as passé. Tu as lancé. Le ballon est orange. Oui. Et le panier est bas. Nina tient le ballon. C'est ton lancer. Elle lance. Le filet bouge. Bien joué. Chacun a un lancer. Nina pose le pied près du panier. Les pieds restent ici. Près du panier. Oui. On passe, puis on lance. Nina passe le ballon. Papa le rend. Nina lance. Le ballon rentre encore. Bravo. Chacun a un lancer. Une feuille de salade tremble. Une goutte est tombée. Oui. Et toi, tu as bien visé. Nina attend. Papa lance. Puis Nina lance. Tu as passé. Tu as lancé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine joue au basket. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina joue au basket. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Yasmine a passé le ballon. Elle a visé le &lt;emphasis level="moderate"&gt;panier&lt;/emphasis&gt;. Chacun a eu un lancer.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a passé le ballon. Elle a visé le panier. Chacun a eu un lancer. Tu as passé. Tu as lancé. Chacun a eu un lancer. Le ballon est allé dans le panier. Oui. Bravo, Nina. Une goutte brille encore sur la salade. Le tuyau vert reste enroulé. Tu as visé le panier. Oui. Chacun un lancer. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa range le ballon. Yasmine essuie ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon. Nina essuie ses mains. Tu as fini de jouer ? Oui, papa. Bravo. On rentre. L'herbe est fraîche sous les pieds. Ils rentrent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le ballon orange est rangé. Nina a passé. Elle a visé le panier. Bravo, Nina. Tu as bien joué. L'histoire est finie.</t>
+          <t>Le ballon orange est rangé. Nina a passé. Elle a visé le panier. Bravo, Nina. Tu as bien joué.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon orange est rangé. Nina a passé. Elle a visé le panier. Bravo, Nina. Tu as bien joué.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,8 +2090,7 @@
         <is>
           <t>narrateur|Le ballon orange est rangé.
 narrateur|Nina a passé. Elle a visé le panier.
-papa|Bravo, Nina. Tu as bien joué.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Nina. Tu as bien joué.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2156,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.BAS.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yasmine, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
